--- a/MSC_Trust_Groceries_Bulk_Import_Template.xlsx
+++ b/MSC_Trust_Groceries_Bulk_Import_Template.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
   <si>
     <t>M.S. CHELLAMUTHU TRUST &amp; RESEARCH FOUNDATION</t>
   </si>
@@ -60,174 +60,6 @@
   </si>
   <si>
     <t>[optional]</t>
-  </si>
-  <si>
-    <t>Rice (Sona Masoori)</t>
-  </si>
-  <si>
-    <t>Kg</t>
-  </si>
-  <si>
-    <t>Annapoorna Traders</t>
-  </si>
-  <si>
-    <t>31/12/2026</t>
-  </si>
-  <si>
-    <t>Main Storeroom</t>
-  </si>
-  <si>
-    <t>Monthly ration stock</t>
-  </si>
-  <si>
-    <t>Toor Dal</t>
-  </si>
-  <si>
-    <t>Sri Murugan Traders</t>
-  </si>
-  <si>
-    <t>31/10/2026</t>
-  </si>
-  <si>
-    <t>Cooking Oil (Sunflower)</t>
-  </si>
-  <si>
-    <t>Litres</t>
-  </si>
-  <si>
-    <t>Fortune Distributors</t>
-  </si>
-  <si>
-    <t>30/06/2027</t>
-  </si>
-  <si>
-    <t>Kitchen Shelf</t>
-  </si>
-  <si>
-    <t>1-litre bottles</t>
-  </si>
-  <si>
-    <t>Salt (Iodised)</t>
-  </si>
-  <si>
-    <t>Sugar</t>
-  </si>
-  <si>
-    <t>31/08/2026</t>
-  </si>
-  <si>
-    <t>Turmeric Powder</t>
-  </si>
-  <si>
-    <t>Local Market</t>
-  </si>
-  <si>
-    <t>30/09/2026</t>
-  </si>
-  <si>
-    <t>Spice Cabinet</t>
-  </si>
-  <si>
-    <t>Red Chilli Powder</t>
-  </si>
-  <si>
-    <t>Mustard Seeds</t>
-  </si>
-  <si>
-    <t>Coconut Oil</t>
-  </si>
-  <si>
-    <t>Nirapara</t>
-  </si>
-  <si>
-    <t>31/03/2027</t>
-  </si>
-  <si>
-    <t>For tempering only</t>
-  </si>
-  <si>
-    <t>Tea Powder</t>
-  </si>
-  <si>
-    <t>Tata Tea</t>
-  </si>
-  <si>
-    <t>31/01/2027</t>
-  </si>
-  <si>
-    <t>Morning/evening tea</t>
-  </si>
-  <si>
-    <t>Milk Powder</t>
-  </si>
-  <si>
-    <t>Packets</t>
-  </si>
-  <si>
-    <t>Aavin</t>
-  </si>
-  <si>
-    <t>30/11/2026</t>
-  </si>
-  <si>
-    <t>Cold Storage</t>
-  </si>
-  <si>
-    <t>50g packets</t>
-  </si>
-  <si>
-    <t>Biscuits (Glucose)</t>
-  </si>
-  <si>
-    <t>Parle</t>
-  </si>
-  <si>
-    <t>30/08/2026</t>
-  </si>
-  <si>
-    <t>Dry Store</t>
-  </si>
-  <si>
-    <t>For children's programme</t>
-  </si>
-  <si>
-    <t>Bread (Sliced)</t>
-  </si>
-  <si>
-    <t>Local Bakery</t>
-  </si>
-  <si>
-    <t>18/07/2026</t>
-  </si>
-  <si>
-    <t>Kitchen Counter</t>
-  </si>
-  <si>
-    <t>Order fresh weekly</t>
-  </si>
-  <si>
-    <t>Eggs</t>
-  </si>
-  <si>
-    <t>Nos</t>
-  </si>
-  <si>
-    <t>Local Farm</t>
-  </si>
-  <si>
-    <t>25/07/2026</t>
-  </si>
-  <si>
-    <t>Banana</t>
-  </si>
-  <si>
-    <t>20/07/2026</t>
-  </si>
-  <si>
-    <t>Fruit Basket</t>
-  </si>
-  <si>
-    <t>For therapy patients</t>
   </si>
   <si>
     <t>REFERENCE GUIDE — Valid values for each column</t>
@@ -347,11 +179,6 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF0F172A"/>
-      <sz val="9"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
@@ -364,13 +191,18 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF0F172A"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FF92400E"/>
       <sz val="9"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -400,11 +232,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF1F5F9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -438,7 +265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -458,31 +285,13 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -793,7 +602,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -903,423 +712,6 @@
       </c>
       <c r="I6" s="6" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="8">
-        <v>50</v>
-      </c>
-      <c r="D7" s="9">
-        <v>42</v>
-      </c>
-      <c r="E7" s="8">
-        <v>20</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="11">
-        <v>25</v>
-      </c>
-      <c r="D8" s="12">
-        <v>95</v>
-      </c>
-      <c r="E8" s="11">
-        <v>10</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="10"/>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="8">
-        <v>20</v>
-      </c>
-      <c r="D9" s="9">
-        <v>140</v>
-      </c>
-      <c r="E9" s="8">
-        <v>8</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="11">
-        <v>10</v>
-      </c>
-      <c r="D10" s="12">
-        <v>22</v>
-      </c>
-      <c r="E10" s="11">
-        <v>5</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="10"/>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="8">
-        <v>15</v>
-      </c>
-      <c r="D11" s="9">
-        <v>48</v>
-      </c>
-      <c r="E11" s="8">
-        <v>5</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="7"/>
-    </row>
-    <row r="12" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="11">
-        <v>2</v>
-      </c>
-      <c r="D12" s="12">
-        <v>85</v>
-      </c>
-      <c r="E12" s="11">
-        <v>1</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I12" s="10"/>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="8">
-        <v>2</v>
-      </c>
-      <c r="D13" s="9">
-        <v>90</v>
-      </c>
-      <c r="E13" s="8">
-        <v>1</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I13" s="7"/>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="11">
-        <v>1</v>
-      </c>
-      <c r="D14" s="12">
-        <v>65</v>
-      </c>
-      <c r="E14" s="11">
-        <v>1</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I14" s="10"/>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="8">
-        <v>5</v>
-      </c>
-      <c r="D15" s="9">
-        <v>180</v>
-      </c>
-      <c r="E15" s="8">
-        <v>2</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="11">
-        <v>3</v>
-      </c>
-      <c r="D16" s="12">
-        <v>220</v>
-      </c>
-      <c r="E16" s="11">
-        <v>1</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="8">
-        <v>6</v>
-      </c>
-      <c r="D17" s="9">
-        <v>310</v>
-      </c>
-      <c r="E17" s="8">
-        <v>2</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="11">
-        <v>24</v>
-      </c>
-      <c r="D18" s="12">
-        <v>10</v>
-      </c>
-      <c r="E18" s="11">
-        <v>12</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="8">
-        <v>8</v>
-      </c>
-      <c r="D19" s="9">
-        <v>45</v>
-      </c>
-      <c r="E19" s="8">
-        <v>4</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="11">
-        <v>60</v>
-      </c>
-      <c r="D20" s="12">
-        <v>7</v>
-      </c>
-      <c r="E20" s="11">
-        <v>30</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="I20" s="10"/>
-    </row>
-    <row r="21" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" s="8">
-        <v>50</v>
-      </c>
-      <c r="D21" s="9">
-        <v>5</v>
-      </c>
-      <c r="E21" s="8">
-        <v>20</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1347,113 +739,113 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>70</v>
+      <c r="A1" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="B1"/>
     </row>
     <row r="2" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>72</v>
+      <c r="A3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>74</v>
+      <c r="A4" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>76</v>
+      <c r="A5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>77</v>
+      <c r="B6" s="9" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="15" t="s">
-        <v>78</v>
+      <c r="B7" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>80</v>
+      <c r="A8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="15" t="s">
-        <v>81</v>
+      <c r="B9" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
-        <v>82</v>
+      <c r="A11" s="10" t="s">
+        <v>26</v>
       </c>
       <c r="B11"/>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>84</v>
+      <c r="A12" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>86</v>
+      <c r="A13" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>88</v>
+      <c r="A14" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>90</v>
+      <c r="A15" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>92</v>
+      <c r="A16" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
